--- a/templates/REGISTRE_HYPOTHESES.xlsx
+++ b/templates/REGISTRE_HYPOTHESES.xlsx
@@ -4,12 +4,14 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="LISEZ_MOI" sheetId="1" r:id="rId1"/>
-    <sheet name="PARAMETRES" sheetId="2" r:id="rId2"/>
-    <sheet name="HYPOTHESES" sheetId="3" r:id="rId3"/>
-    <sheet name="EVENEMENTS" sheetId="4" r:id="rId4"/>
-    <sheet name="CORRELATIONS" sheetId="5" r:id="rId5"/>
-    <sheet name="LEVIERS" sheetId="6" r:id="rId6"/>
-    <sheet name="STRESS" sheetId="7" r:id="rId7"/>
+    <sheet name="GUIDE" sheetId="2" r:id="rId2"/>
+    <sheet name="PARAMETRES" sheetId="3" r:id="rId3"/>
+    <sheet name="HYPOTHESES" sheetId="4" r:id="rId4"/>
+    <sheet name="EVENEMENTS" sheetId="5" r:id="rId5"/>
+    <sheet name="CORRELATIONS" sheetId="6" r:id="rId6"/>
+    <sheet name="REVUE_RISQUES" sheetId="7" r:id="rId7"/>
+    <sheet name="LEVIERS" sheetId="8" r:id="rId8"/>
+    <sheet name="STRESS" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -403,7 +405,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -425,14 +427,350 @@
         <v>H07 se saisit par P10 et P90 (loi lognormale, P50 vide) ; H06 par départ, dérive annuelle et volatilité mensuelle (marche aléatoire) ; renseigner min et max pour une loi PERT.</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Feuille GUIDE : la question à poser à chaque propriétaire, où chercher la réponse, le piège à éviter. Feuille REVUE_RISQUES : une décision par catégorie de risque, pour ne rien oublier.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F16"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>libelle</v>
+      </c>
+      <c r="C1" t="str">
+        <v>question</v>
+      </c>
+      <c r="D1" t="str">
+        <v>qui_repond</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sources</v>
+      </c>
+      <c r="F1" t="str">
+        <v>piege</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>H01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Volume Boissons</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Par rapport au volume budgété, où serait le volume Boissons dans une mauvaise année (1 chance sur 10), une année normale, une bonne année (1 chance sur 10) ?</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Directeur commercial de la BU</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Volumes réalisés des 5 derniers exercices, carnet de commandes, référencements signés, tendance du marché.</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Ne pas y compter la perte d'un grand compte : elle est portée par l'événement E02, sinon elle est comptée deux fois.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>H02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Volume Épicerie</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Par rapport au volume budgété, où serait le volume Épicerie dans une mauvaise année, une année normale, une bonne année ?</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Directeur commercial de la BU</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Volumes réalisés des 5 derniers exercices, référencements signés, carnet de commandes.</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Ne pas y compter la perte d'un grand compte (E02) ni une rupture d'approvisionnement (E03).</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>H03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Volume Hygiène</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Par rapport au volume budgété, où serait le volume Hygiène dans une mauvaise année, une année normale, une bonne année ?</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Directeur commercial de la BU</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Volumes réalisés des 5 derniers exercices, part de marché, lancements prévus.</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Une fourchette symétrique n'est pas obligatoire : si le risque baissier est plus grand, la fourchette doit le montrer.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>H04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Prix net réalisé</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Quel prix net moyen sera réellement encaissé par rapport au prix budgété, une fois remises et promotions déduites ?</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Directeur commercial</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Hausses tarifaires négociées, historique des remises par enseigne, conditions générales de vente.</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Raisonner en prix net réalisé, pas en prix catalogue : les remises de fin d'année font souvent la différence.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>H05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Mix produits et canaux</v>
+      </c>
+      <c r="C6" t="str">
+        <v>De combien de points la marge brute peut-elle s'écarter du budget à cause du mix produits et canaux ?</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Contrôle de gestion</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Écarts de mix des 3 derniers exercices, plan de lancement des produits.</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Saisir en points de marge brute (0,4 = 0,4 point), pas en pourcentage du chiffre d'affaires.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>H06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Change EUR/MGA, cours moyen</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Quel cours EUR/MGA au départ, quelle dérive annuelle attendue, quelle volatilité mensuelle ?</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Trésorerie</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Dernier cours connu, 60 derniers mois de cours, prévisions des banques.</v>
+      </c>
+      <c r="F7" t="str">
+        <v>La volatilité mensuelle se lit sur l'historique des variations mensuelles, pas sur l'écart entre deux cours éloignés.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>H07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Prix d'achat importés, en EUR</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Où seraient les prix d'achat des produits importés, en euros, dans une année défavorable et une année favorable ?</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Contrats fournisseurs, clauses d'indexation, cours mondiaux des matières.</v>
+      </c>
+      <c r="F8" t="str">
+        <v>En euros, hors change : l'effet du cours EUR/MGA est déjà porté par H06.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>H08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Prix d'achat locaux</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Où seraient les prix d'achat locaux par rapport au budget, dans une mauvaise année, une année normale, une bonne année ?</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Inflation domestique, contrats locaux, historique des hausses fournisseurs.</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Une dépréciation de l'ariary fait monter les prix locaux : relier H08 à H06 par une corrélation plutôt que d'élargir la fourchette.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>H09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Tarifs transporteurs</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Où seraient les tarifs des transporteurs par rapport au budget, hors révision exceptionnelle du carburant ?</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Supply chain</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Contrats de transport, dates de renégociation, historique des révisions.</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Une révision brutale du prix du carburant est portée par E01 : ne pas la compter aussi ici.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>H10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Masse salariale</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Où serait la masse salariale par rapport au budget : rattrapage d'inflation, embauches, primes ?</v>
+      </c>
+      <c r="D11" t="str">
+        <v>RH</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Accord salarial, plan d'embauche, historique des augmentations.</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Penser au rattrapage salarial si l'inflation dépasse l'hypothèse du budget.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>H11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Frais commerciaux</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Où seraient les frais commerciaux par rapport au budget, y compris les relances promotionnelles si les volumes décrochent ?</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Plan promotionnel, accords de coopération commerciale, historique des dépassements.</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Les relances suivent souvent une baisse de volume : la corrélation négative avec les volumes doit le dire.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>H12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Frais généraux</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Où seraient les frais généraux par rapport au budget : énergie, maintenance, informatique ?</v>
+      </c>
+      <c r="D13" t="str">
+        <v>DAF</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Contrats, factures d'énergie, plan informatique.</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Une partie de ces frais est payée en devises : la relier au change plutôt que d'élargir la fourchette.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>E01</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Révision du prix du carburant</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Quelle chance qu'une révision du prix du carburant survienne dans l'année, et de combien serait-elle ?</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Supply chain</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Révisions des 5 à 10 dernières années : leur nombre donne la fréquence, leur ampleur donne l'amplitude.</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Fréquence = nombre d'années avec révision divisé par le nombre d'années observées, pas le nombre de révisions.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>E02</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Perte d'un grand compte GMS</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Quelle chance de perdre un grand compte dans l'année, et quelle part des volumes représenterait-il ?</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Directeur commercial</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Pertes de comptes des 5 dernières années, comptes en renégociation, poids de chaque grand compte.</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Si un compte est déjà perdu ou annoncé perdu, ce n'est plus un risque : il doit sortir du budget.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>E03</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Retard de navire (effet bateau)</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Quelle chance qu'un retard de navire provoque une rupture, combien de ventes seraient perdues ce mois-là, et quel surcoût ?</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Supply chain</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Journal des ruptures, historique des retards portuaires, stock de sécurité.</v>
+      </c>
+      <c r="F16" t="str">
+        <v>L'amplitude est la part des ventes perdues sur le mois touché, pas sur l'année.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F16"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
   <sheetData>
@@ -507,7 +845,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:P13"/>
   <sheetData>
@@ -985,7 +1323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L4"/>
   <sheetData>
@@ -1136,7 +1474,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D19"/>
   <sheetData>
@@ -1413,7 +1751,363 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:F19"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>categorie</v>
+      </c>
+      <c r="B1" t="str">
+        <v>libelle</v>
+      </c>
+      <c r="C1" t="str">
+        <v>question</v>
+      </c>
+      <c r="D1" t="str">
+        <v>decision</v>
+      </c>
+      <c r="E1" t="str">
+        <v>reference</v>
+      </c>
+      <c r="F1" t="str">
+        <v>commentaire</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>R01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Volumes et demande</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Le marché, la saisonnalité ou la météo peuvent-ils faire décrocher les volumes ?</v>
+      </c>
+      <c r="D2" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E2" t="str">
+        <v>H01, H02, H03</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Tendance et dispersion des 5 derniers exercices par BU.</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>R02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Prix de vente et remises</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Les clients peuvent-ils imposer des remises ou refuser une hausse ?</v>
+      </c>
+      <c r="D3" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E3" t="str">
+        <v>H04</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Hausse de janvier négociée ; remises GMS dans la fourchette.</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>R03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Mix produits et canaux</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Le poids des produits ou des canaux à faible marge peut-il augmenter ?</v>
+      </c>
+      <c r="D4" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E4" t="str">
+        <v>H05</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Écarts de mix observés sur 3 exercices.</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>R04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Change</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Une dépréciation de la monnaie locale renchérit-elle les achats ?</v>
+      </c>
+      <c r="D5" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E5" t="str">
+        <v>H06</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Marche aléatoire calibrée sur 60 mois, corrélée aux achats et aux frais.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>R05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Coût des achats</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Les prix fournisseurs, importés ou locaux, peuvent-ils monter plus que prévu ?</v>
+      </c>
+      <c r="D6" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E6" t="str">
+        <v>H07, H08</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Contrats annuels et inflation domestique.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>R06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Transport et logistique</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Le carburant, les tarifs transporteurs ou les délais d'acheminement peuvent-ils déraper ?</v>
+      </c>
+      <c r="D7" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E7" t="str">
+        <v>H09, E01, E03</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Tarifs, révision du carburant et retards de navire.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>R07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Masse salariale et climat social</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Un rattrapage salarial, des embauches ou un conflit social sont-ils possibles ?</v>
+      </c>
+      <c r="D8" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E8" t="str">
+        <v>H10</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Accord salarial signé ; rattrapage possible si l'inflation dérape.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>R08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Frais commerciaux et généraux</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Des dépenses de relance, d'énergie ou d'informatique peuvent-elles dépasser le budget ?</v>
+      </c>
+      <c r="D9" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E9" t="str">
+        <v>H11, H12</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Plan promotionnel et frais sensibles au change.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>R09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Client clé et impayés</v>
+      </c>
+      <c r="C10" t="str">
+        <v>La perte ou la défaillance d'un grand client toucherait-elle l'EBITDA ?</v>
+      </c>
+      <c r="D10" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E10" t="str">
+        <v>E02</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Perte d'un grand compte GMS ; impayés historiquement négligeables.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>R10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Fournisseur clé et ruptures</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Un fournisseur unique peut-il faire défaut, ou un retard créer des ruptures ?</v>
+      </c>
+      <c r="D11" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E11" t="str">
+        <v>E03</v>
+      </c>
+      <c r="F11" t="str">
+        <v>Retards de navire ; pas de fournisseur unique hors importations.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>R11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Fiscalité, douanes, réglementation</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Droits de douane, taxes, prix administrés ou normes peuvent-ils changer en cours d'année ?</v>
+      </c>
+      <c r="D12" t="str">
+        <v>hors-modele</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Hausse des droits de douane évoquée pour la loi de finances 2027, non chiffrable à ce stade : suivie au CODIR.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>R12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Climat et événements naturels</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Cyclone, inondation, sécheresse : quel effet sur les ventes et la logistique ?</v>
+      </c>
+      <c r="D13" t="str">
+        <v>hors-modele</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>Saison cyclonique : effet logistique en partie porté par E03, effet sur la demande non modélisé.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>R13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Énergie et infrastructures</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Des coupures d'électricité ou une hausse de l'énergie toucheraient-elles l'activité ?</v>
+      </c>
+      <c r="D14" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E14" t="str">
+        <v>H12</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Énergie dans les frais généraux ; groupes électrogènes sur les deux entrepôts.</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>R14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Informatique, cyber, fraude</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Une panne, une attaque ou une fraude pourraient-elles arrêter la facturation ?</v>
+      </c>
+      <c r="D15" t="str">
+        <v>non-significatif</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v>Facturation sur logiciel hébergé avec reprise sous 24 heures : impact jugé inférieur à 10 MAr.</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>R15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Concurrence</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Un nouvel entrant ou une guerre des prix sont-ils plausibles cette année ?</v>
+      </c>
+      <c r="D16" t="str">
+        <v>couvert</v>
+      </c>
+      <c r="E16" t="str">
+        <v>H04, E02</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Pression concurrentielle dans la fourchette de prix et la perte de grand compte.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>R16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Risques sous l'EBITDA</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Taux d'intérêt, impôt, dépréciations : ils ne changent pas l'EBITDA, le confirmer.</v>
+      </c>
+      <c r="D17" t="str">
+        <v>non-significatif</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v>Taux, impôt et dépréciations sont sous l'EBITDA : sans effet sur l'indicateur suivi.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Décisions possibles : couvert, stress, non-significatif, hors-modele.</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:F19"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K6"/>
   <sheetData>
@@ -1634,7 +2328,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E4"/>
   <sheetData>

--- a/templates/REGISTRE_HYPOTHESES.xlsx
+++ b/templates/REGISTRE_HYPOTHESES.xlsx
@@ -4,14 +4,16 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="LISEZ_MOI" sheetId="1" r:id="rId1"/>
-    <sheet name="GUIDE" sheetId="2" r:id="rId2"/>
-    <sheet name="PARAMETRES" sheetId="3" r:id="rId3"/>
-    <sheet name="HYPOTHESES" sheetId="4" r:id="rId4"/>
-    <sheet name="EVENEMENTS" sheetId="5" r:id="rId5"/>
-    <sheet name="CORRELATIONS" sheetId="6" r:id="rId6"/>
-    <sheet name="REVUE_RISQUES" sheetId="7" r:id="rId7"/>
-    <sheet name="LEVIERS" sheetId="8" r:id="rId8"/>
-    <sheet name="STRESS" sheetId="9" r:id="rId9"/>
+    <sheet name="REFERENTIEL" sheetId="2" r:id="rId2"/>
+    <sheet name="GUIDE" sheetId="3" r:id="rId3"/>
+    <sheet name="PARAMETRES" sheetId="4" r:id="rId4"/>
+    <sheet name="HYPOTHESES" sheetId="5" r:id="rId5"/>
+    <sheet name="EVENEMENTS" sheetId="6" r:id="rId6"/>
+    <sheet name="CORRELATIONS" sheetId="7" r:id="rId7"/>
+    <sheet name="REVUE_RISQUES" sheetId="8" r:id="rId8"/>
+    <sheet name="LEVIERS" sheetId="9" r:id="rId9"/>
+    <sheet name="STRESS" sheetId="10" r:id="rId10"/>
+    <sheet name="PAQUETS" sheetId="11" r:id="rId11"/>
   </sheets>
 </workbook>
 </file>
@@ -405,11 +407,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>REGISTRE_HYPOTHESES : hypothèses, événements, corrélations, leviers. À rééditer puis réimporter.</v>
+        <v>REGISTRE_HYPOTHESES : hypothèses, événements, corrélations, leviers, stress tests. À rééditer puis réimporter : on peut ajouter ou retirer des lignes.</v>
       </c>
     </row>
     <row r="2">
@@ -419,27 +421,589 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Règles : P10 &lt; P50 &lt; P90 (R-HY-01) ; un propriétaire et une justification par ligne (principe 3) ; corrélations de rang entre -0,9 et +0,9 (R-DE-01).</v>
+        <v>Règles : P10 &lt; P50 &lt; P90 (R-HY-01) ; un propriétaire et une justification par ligne (principe 3) ; corrélations de rang entre -0,9 et +0,9 (R-DE-01) ; codes uniques.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>H07 se saisit par P10 et P90 (loi lognormale, P50 vide) ; H06 par départ, dérive annuelle et volatilité mensuelle (marche aléatoire) ; renseigner min et max pour une loi PERT.</v>
+        <v>Effet d'une hypothèse : volume, prix, poste, change, marge. Volume et prix : facteurs (1 = budget) sur les BU visées ; poste : facteur sur les postes visés ; marge : points de marge sur le CA, ajoutés à une rubrique ; change : départ, dérive annuelle et volatilité mensuelle (marche aléatoire).</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Feuille GUIDE : la question à poser à chaque propriétaire, où chercher la réponse, le piège à éviter. Feuille REVUE_RISQUES : une décision par catégorie de risque, pour ne rien oublier.</v>
+        <v>Lognormale : laisser p50 vide et saisir P10 et P90. PERT : renseigner min et max, p50 étant le mode.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Colonne porte_sur : « bu: Boissons, Epicerie », « postes: CARBURANT, SOUS_TRAITANCE », « rubrique: FG », « hypothese: H09 », « evenement: E03 », plusieurs parties séparées par « ; ». Vide : toute l'entreprise.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Feuille REFERENTIEL : les BU, rubriques et postes du budget, à citer dans porte_sur. Feuille GUIDE : la question à poser à chaque propriétaire.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G6"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>libelle</v>
+      </c>
+      <c r="C1" t="str">
+        <v>type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>porte_sur</v>
+      </c>
+      <c r="E1" t="str">
+        <v>regle</v>
+      </c>
+      <c r="F1" t="str">
+        <v>mois_effet</v>
+      </c>
+      <c r="G1" t="str">
+        <v>parametres</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>S1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Dépréciation brutale de l'ariary</v>
+      </c>
+      <c r="C2" t="str">
+        <v>change</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v>Cours +15 % au-dessus de la trajectoire simulée, dès avril</v>
+      </c>
+      <c r="F2">
+        <v>4</v>
+      </c>
+      <c r="G2" t="str">
+        <v>choc=0.15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>S2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Perte de deux grands comptes GMS</v>
+      </c>
+      <c r="C3" t="str">
+        <v>evenement</v>
+      </c>
+      <c r="D3" t="str">
+        <v>evenement: E02</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Volumes Boissons et Épicerie -12 % dès avril (E02 forcé)</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3" t="str">
+        <v>choc=0.12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Choc carburant</v>
+      </c>
+      <c r="C4" t="str">
+        <v>poste</v>
+      </c>
+      <c r="D4" t="str">
+        <v>postes: CARBURANT</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Carburant +25 % dès avril, en plus des révisions simulées</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4" t="str">
+        <v>choc=0.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Types : change (choc) ; evenement (choc) ; poste (choc) ; volume (choc).</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:G6"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>libelle</v>
+      </c>
+      <c r="C1" t="str">
+        <v>composition</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>A</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Paquet A : L2 + L3</v>
+      </c>
+      <c r="C2" t="str">
+        <v>L2; L3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>B</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Paquet B : A + L1</v>
+      </c>
+      <c r="C3" t="str">
+        <v>L1; L2; L3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>S1+S3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Choc macro combiné</v>
+      </c>
+      <c r="C4" t="str">
+        <v>S1; S3</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D27"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>type</v>
+      </c>
+      <c r="B1" t="str">
+        <v>code</v>
+      </c>
+      <c r="C1" t="str">
+        <v>libelle</v>
+      </c>
+      <c r="D1" t="str">
+        <v>detail</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>bu</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Boissons</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Boissons</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>bu</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Epicerie</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Epicerie</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>bu</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Hygiene</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Hygiene</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B5" t="str">
+        <v>CA</v>
+      </c>
+      <c r="C5" t="str">
+        <v>CA net</v>
+      </c>
+      <c r="D5" t="str">
+        <v>ca</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B6" t="str">
+        <v>CM</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Coût matière</v>
+      </c>
+      <c r="D6" t="str">
+        <v>charge</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B7" t="str">
+        <v>MIX</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Effet mix</v>
+      </c>
+      <c r="D7" t="str">
+        <v>produit</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B8" t="str">
+        <v>TR</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Transport</v>
+      </c>
+      <c r="D8" t="str">
+        <v>charge</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B9" t="str">
+        <v>MS</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Masse salariale</v>
+      </c>
+      <c r="D9" t="str">
+        <v>charge</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B10" t="str">
+        <v>FC</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Frais commerciaux</v>
+      </c>
+      <c r="D10" t="str">
+        <v>charge</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>rubrique</v>
+      </c>
+      <c r="B11" t="str">
+        <v>FG</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Frais généraux</v>
+      </c>
+      <c r="D11" t="str">
+        <v>charge</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B12" t="str">
+        <v>CA_Boissons</v>
+      </c>
+      <c r="C12" t="str">
+        <v>CA Boissons</v>
+      </c>
+      <c r="D12" t="str">
+        <v>CA, BU Boissons, assiette volume</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B13" t="str">
+        <v>CA_Epicerie</v>
+      </c>
+      <c r="C13" t="str">
+        <v>CA Epicerie</v>
+      </c>
+      <c r="D13" t="str">
+        <v>CA, BU Epicerie, assiette volume</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B14" t="str">
+        <v>CA_Hygiene</v>
+      </c>
+      <c r="C14" t="str">
+        <v>CA Hygiene</v>
+      </c>
+      <c r="D14" t="str">
+        <v>CA, BU Hygiene, assiette volume</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B15" t="str">
+        <v>CMI_Boissons</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Coût matière importé Boissons</v>
+      </c>
+      <c r="D15" t="str">
+        <v>CM, BU Boissons, assiette volume, 100 % en devises</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B16" t="str">
+        <v>CML_Boissons</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Coût matière local Boissons</v>
+      </c>
+      <c r="D16" t="str">
+        <v>CM, BU Boissons, assiette volume</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B17" t="str">
+        <v>CMI_Epicerie</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Coût matière importé Epicerie</v>
+      </c>
+      <c r="D17" t="str">
+        <v>CM, BU Epicerie, assiette volume, 100 % en devises</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B18" t="str">
+        <v>CML_Epicerie</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Coût matière local Epicerie</v>
+      </c>
+      <c r="D18" t="str">
+        <v>CM, BU Epicerie, assiette volume</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B19" t="str">
+        <v>CMI_Hygiene</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Coût matière importé Hygiene</v>
+      </c>
+      <c r="D19" t="str">
+        <v>CM, BU Hygiene, assiette volume, 100 % en devises</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B20" t="str">
+        <v>CML_Hygiene</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Coût matière local Hygiene</v>
+      </c>
+      <c r="D20" t="str">
+        <v>CM, BU Hygiene, assiette volume</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B21" t="str">
+        <v>CARBURANT</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Carburant de la flotte</v>
+      </c>
+      <c r="D21" t="str">
+        <v>TR, commun, assiette volume</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SOUS_TRAITANCE</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Transport sous-traité</v>
+      </c>
+      <c r="D22" t="str">
+        <v>TR, commun, assiette volume</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B23" t="str">
+        <v>AUTRES_TRANSPORT</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Autres frais de transport</v>
+      </c>
+      <c r="D23" t="str">
+        <v>TR, commun, assiette fixe</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B24" t="str">
+        <v>MASSE_SALARIALE</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Masse salariale</v>
+      </c>
+      <c r="D24" t="str">
+        <v>MS, commun, assiette fixe</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B25" t="str">
+        <v>FC_VARIABLES</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Frais commerciaux variables</v>
+      </c>
+      <c r="D25" t="str">
+        <v>FC, commun, assiette ca</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B26" t="str">
+        <v>FC_FIXES</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Frais commerciaux fixes</v>
+      </c>
+      <c r="D26" t="str">
+        <v>FC, commun, assiette fixe</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>poste</v>
+      </c>
+      <c r="B27" t="str">
+        <v>FRAIS_GENERAUX</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Frais généraux</v>
+      </c>
+      <c r="D27" t="str">
+        <v>FG, commun, assiette fixe</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D27"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F16"/>
   <sheetData>
@@ -770,9 +1334,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -832,500 +1396,30 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>postes_certains</v>
+      </c>
+      <c r="B8" t="str">
+        <v>AUTRES_TRANSPORT</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
         <v>version_outil</v>
       </c>
-      <c r="B8" t="str">
+      <c r="B9" t="str">
         <v>1.0.0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B8"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P13"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>code</v>
-      </c>
-      <c r="B1" t="str">
-        <v>libelle</v>
-      </c>
-      <c r="C1" t="str">
-        <v>proprietaire</v>
-      </c>
-      <c r="D1" t="str">
-        <v>unite</v>
-      </c>
-      <c r="E1" t="str">
-        <v>grain</v>
-      </c>
-      <c r="F1" t="str">
-        <v>p10</v>
-      </c>
-      <c r="G1" t="str">
-        <v>p50</v>
-      </c>
-      <c r="H1" t="str">
-        <v>p90</v>
-      </c>
-      <c r="I1" t="str">
-        <v>min</v>
-      </c>
-      <c r="J1" t="str">
-        <v>max</v>
-      </c>
-      <c r="K1" t="str">
-        <v>depart</v>
-      </c>
-      <c r="L1" t="str">
-        <v>derive_annuelle</v>
-      </c>
-      <c r="M1" t="str">
-        <v>volatilite_mensuelle</v>
-      </c>
-      <c r="N1" t="str">
-        <v>k</v>
-      </c>
-      <c r="O1" t="str">
-        <v>justification</v>
-      </c>
-      <c r="P1" t="str">
-        <v>statut</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>H01</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Volume Boissons</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Directeur commercial Boissons</v>
-      </c>
-      <c r="D2" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E2" t="str">
-        <v>BU Boissons, tous canaux</v>
-      </c>
-      <c r="F2">
-        <v>0.955</v>
-      </c>
-      <c r="G2">
-        <v>0.995</v>
-      </c>
-      <c r="H2">
-        <v>1.025</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Tendance 5 ans, élasticité prix, carnet de commandes GMS. Perte de grand compte exclue (portée par E02).</v>
-      </c>
-      <c r="P2" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>H02</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Volume Épicerie</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Directeur commercial Épicerie</v>
-      </c>
-      <c r="D3" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E3" t="str">
-        <v>BU Épicerie, tous canaux</v>
-      </c>
-      <c r="F3">
-        <v>0.965</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1.025</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Tendance 5 ans, référencements 2027 signés. Perte de grand compte exclue (portée par E02).</v>
-      </c>
-      <c r="P3" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>H03</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Volume Hygiène</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Directeur commercial Hygiène</v>
-      </c>
-      <c r="D4" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E4" t="str">
-        <v>BU Hygiène, tous canaux</v>
-      </c>
-      <c r="F4">
-        <v>0.96</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1.04</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Marché stable, dispersion historique symétrique sur 5 ans.</v>
-      </c>
-      <c r="P4" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>H04</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Prix net réalisé</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Directeur commercial</v>
-      </c>
-      <c r="D5" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E5" t="str">
-        <v>total</v>
-      </c>
-      <c r="F5">
-        <v>0.99</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1.005</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Hausse tarifaire de janvier négociée ; risque de remises supplémentaires en GMS.</v>
-      </c>
-      <c r="P5" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>H05</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Mix produits et canaux</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Contrôle de gestion</v>
-      </c>
-      <c r="D6" t="str">
-        <v>points de marge brute</v>
-      </c>
-      <c r="E6" t="str">
-        <v>total</v>
-      </c>
-      <c r="F6">
-        <v>-0.4</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0.4</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Écarts de mix observés sur 3 exercices, symétriques.</v>
-      </c>
-      <c r="P6" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>H06</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Change EUR/MGA, cours moyen</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Trésorerie</v>
-      </c>
-      <c r="D7" t="str">
-        <v>MGA pour 1 EUR</v>
-      </c>
-      <c r="E7" t="str">
-        <v>total</v>
-      </c>
-      <c r="K7">
-        <v>5100</v>
-      </c>
-      <c r="L7">
-        <v>0.04</v>
-      </c>
-      <c r="M7">
-        <v>0.018</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Dernier cours connu 5 100 ; dérive et volatilité estimées sur 60 mois.</v>
-      </c>
-      <c r="P7" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>H07</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Prix d'achat importés, en EUR</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Achats</v>
-      </c>
-      <c r="D8" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E8" t="str">
-        <v>total</v>
-      </c>
-      <c r="F8">
-        <v>0.98</v>
-      </c>
-      <c r="H8">
-        <v>1.025</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Contrats fournisseurs annuels, indexation partielle sur les cours mondiaux.</v>
-      </c>
-      <c r="P8" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>H08</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Prix d'achat locaux</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Achats</v>
-      </c>
-      <c r="D9" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E9" t="str">
-        <v>total</v>
-      </c>
-      <c r="F9">
-        <v>0.99</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1.02</v>
-      </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-      <c r="O9" t="str">
-        <v>Inflation domestique, en partie importée.</v>
-      </c>
-      <c r="P9" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>H09</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Tarifs transporteurs</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Supply chain</v>
-      </c>
-      <c r="D10" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E10" t="str">
-        <v>total</v>
-      </c>
-      <c r="F10">
-        <v>0.995</v>
-      </c>
-      <c r="G10">
-        <v>1.01</v>
-      </c>
-      <c r="H10">
-        <v>1.04</v>
-      </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-      <c r="O10" t="str">
-        <v>Renégociation annuelle ; carburant et pièces importés.</v>
-      </c>
-      <c r="P10" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>H10</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Masse salariale</v>
-      </c>
-      <c r="C11" t="str">
-        <v>RH</v>
-      </c>
-      <c r="D11" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E11" t="str">
-        <v>total</v>
-      </c>
-      <c r="F11">
-        <v>0.995</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1.015</v>
-      </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-      <c r="O11" t="str">
-        <v>Accord salarial signé ; risque de rattrapage en cas d'inflation.</v>
-      </c>
-      <c r="P11" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>H11</v>
-      </c>
-      <c r="B12" t="str">
-        <v>Frais commerciaux</v>
-      </c>
-      <c r="C12" t="str">
-        <v>Marketing</v>
-      </c>
-      <c r="D12" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E12" t="str">
-        <v>total</v>
-      </c>
-      <c r="F12">
-        <v>0.97</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12">
-        <v>1.04</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-      <c r="O12" t="str">
-        <v>Plan promotionnel ; relances possibles si les volumes décrochent.</v>
-      </c>
-      <c r="P12" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>H12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Frais généraux</v>
-      </c>
-      <c r="C13" t="str">
-        <v>DAF</v>
-      </c>
-      <c r="D13" t="str">
-        <v>facteur</v>
-      </c>
-      <c r="E13" t="str">
-        <v>total</v>
-      </c>
-      <c r="F13">
-        <v>0.99</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13">
-        <v>1.03</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Énergie, maintenance, informatique : sensibles au change.</v>
-      </c>
-      <c r="P13" t="str">
-        <v>valide</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:S13"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1335,146 +1429,801 @@
         <v>libelle</v>
       </c>
       <c r="C1" t="str">
+        <v>famille</v>
+      </c>
+      <c r="D1" t="str">
+        <v>effet</v>
+      </c>
+      <c r="E1" t="str">
+        <v>porte_sur</v>
+      </c>
+      <c r="F1" t="str">
         <v>proprietaire</v>
       </c>
-      <c r="D1" t="str">
-        <v>p</v>
-      </c>
-      <c r="E1" t="str">
-        <v>amplitude_min</v>
-      </c>
-      <c r="F1" t="str">
-        <v>amplitude_max</v>
-      </c>
       <c r="G1" t="str">
-        <v>surcout_min_gar</v>
+        <v>unite</v>
       </c>
       <c r="H1" t="str">
-        <v>surcout_max_gar</v>
+        <v>grain</v>
       </c>
       <c r="I1" t="str">
-        <v>duree</v>
+        <v>p10</v>
       </c>
       <c r="J1" t="str">
-        <v>cible</v>
+        <v>p50</v>
       </c>
       <c r="K1" t="str">
+        <v>p90</v>
+      </c>
+      <c r="L1" t="str">
+        <v>min</v>
+      </c>
+      <c r="M1" t="str">
+        <v>max</v>
+      </c>
+      <c r="N1" t="str">
+        <v>depart</v>
+      </c>
+      <c r="O1" t="str">
+        <v>derive_annuelle</v>
+      </c>
+      <c r="P1" t="str">
+        <v>volatilite_mensuelle</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>k</v>
+      </c>
+      <c r="R1" t="str">
         <v>justification</v>
       </c>
-      <c r="L1" t="str">
+      <c r="S1" t="str">
         <v>statut</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>E01</v>
+        <v>H01</v>
       </c>
       <c r="B2" t="str">
-        <v>Révision du prix du carburant</v>
+        <v>Volume Boissons</v>
       </c>
       <c r="C2" t="str">
-        <v>Supply chain</v>
-      </c>
-      <c r="D2">
-        <v>0.35</v>
-      </c>
-      <c r="E2">
-        <v>0.08</v>
-      </c>
-      <c r="F2">
-        <v>0.15</v>
-      </c>
-      <c r="I2" t="str">
-        <v>fin</v>
-      </c>
-      <c r="J2" t="str">
-        <v>carburant de la flotte propre</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Environ 0,4 révision par an sur 5 ans, de +8 % à +15 %.</v>
-      </c>
-      <c r="L2" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D2" t="str">
+        <v>volume</v>
+      </c>
+      <c r="E2" t="str">
+        <v>bu: Boissons</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Directeur commercial Boissons</v>
+      </c>
+      <c r="G2" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H2" t="str">
+        <v>BU Boissons, tous canaux</v>
+      </c>
+      <c r="I2">
+        <v>0.955</v>
+      </c>
+      <c r="J2">
+        <v>0.995</v>
+      </c>
+      <c r="K2">
+        <v>1.025</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Tendance 5 ans, élasticité prix, carnet de commandes GMS. Perte de grand compte exclue (portée par E02).</v>
+      </c>
+      <c r="S2" t="str">
         <v>valide</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>E02</v>
+        <v>H02</v>
       </c>
       <c r="B3" t="str">
-        <v>Perte d'un grand compte GMS</v>
+        <v>Volume Épicerie</v>
       </c>
       <c r="C3" t="str">
-        <v>Directeur commercial</v>
-      </c>
-      <c r="D3">
-        <v>0.15</v>
-      </c>
-      <c r="E3">
-        <v>0.04</v>
-      </c>
-      <c r="F3">
-        <v>0.08</v>
-      </c>
-      <c r="I3" t="str">
-        <v>fin</v>
-      </c>
-      <c r="J3" t="str">
-        <v>volumes Boissons et Épicerie</v>
-      </c>
-      <c r="K3" t="str">
-        <v>Deux pertes de comptes en 5 ans, poids de 4 % à 8 % des volumes.</v>
-      </c>
-      <c r="L3" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D3" t="str">
+        <v>volume</v>
+      </c>
+      <c r="E3" t="str">
+        <v>bu: Epicerie</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Directeur commercial Épicerie</v>
+      </c>
+      <c r="G3" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H3" t="str">
+        <v>BU Épicerie, tous canaux</v>
+      </c>
+      <c r="I3">
+        <v>0.965</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1.025</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Tendance 5 ans, référencements 2027 signés. Perte de grand compte exclue (portée par E02).</v>
+      </c>
+      <c r="S3" t="str">
         <v>valide</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>E03</v>
+        <v>H03</v>
       </c>
       <c r="B4" t="str">
-        <v>Retard de navire (effet bateau)</v>
+        <v>Volume Hygiène</v>
       </c>
       <c r="C4" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D4" t="str">
+        <v>volume</v>
+      </c>
+      <c r="E4" t="str">
+        <v>bu: Hygiene</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Directeur commercial Hygiène</v>
+      </c>
+      <c r="G4" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H4" t="str">
+        <v>BU Hygiène, tous canaux</v>
+      </c>
+      <c r="I4">
+        <v>0.96</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1.04</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Marché stable, dispersion historique symétrique sur 5 ans.</v>
+      </c>
+      <c r="S4" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>H04</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Prix net réalisé</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D5" t="str">
+        <v>prix</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v>Directeur commercial</v>
+      </c>
+      <c r="G5" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H5" t="str">
+        <v>total</v>
+      </c>
+      <c r="I5">
+        <v>0.99</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1.005</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Hausse tarifaire de janvier négociée ; risque de remises supplémentaires en GMS.</v>
+      </c>
+      <c r="S5" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>H05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Mix produits et canaux</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D6" t="str">
+        <v>marge</v>
+      </c>
+      <c r="E6" t="str">
+        <v>rubrique: MIX</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Contrôle de gestion</v>
+      </c>
+      <c r="G6" t="str">
+        <v>points de marge brute</v>
+      </c>
+      <c r="H6" t="str">
+        <v>total</v>
+      </c>
+      <c r="I6">
+        <v>-0.4</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0.4</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6" t="str">
+        <v>Écarts de mix observés sur 3 exercices, symétriques.</v>
+      </c>
+      <c r="S6" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>H06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Change EUR/MGA, cours moyen</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Macroéconomie</v>
+      </c>
+      <c r="D7" t="str">
+        <v>change</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Trésorerie</v>
+      </c>
+      <c r="G7" t="str">
+        <v>MGA pour 1 EUR</v>
+      </c>
+      <c r="H7" t="str">
+        <v>total</v>
+      </c>
+      <c r="N7">
+        <v>5100</v>
+      </c>
+      <c r="O7">
+        <v>0.04</v>
+      </c>
+      <c r="P7">
+        <v>0.018</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7" t="str">
+        <v>Dernier cours connu 5 100 ; dérive et volatilité estimées sur 60 mois.</v>
+      </c>
+      <c r="S7" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>H07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Prix d'achat importés, en EUR</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Approvisionnement</v>
+      </c>
+      <c r="D8" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E8" t="str">
+        <v>postes: CMI_Boissons, CMI_Epicerie, CMI_Hygiene</v>
+      </c>
+      <c r="F8" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G8" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H8" t="str">
+        <v>total</v>
+      </c>
+      <c r="I8">
+        <v>0.98</v>
+      </c>
+      <c r="K8">
+        <v>1.025</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Contrats fournisseurs annuels, indexation partielle sur les cours mondiaux.</v>
+      </c>
+      <c r="S8" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>H08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Prix d'achat locaux</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Macroéconomie</v>
+      </c>
+      <c r="D9" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E9" t="str">
+        <v>postes: CML_Boissons, CML_Epicerie, CML_Hygiene</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Achats</v>
+      </c>
+      <c r="G9" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H9" t="str">
+        <v>total</v>
+      </c>
+      <c r="I9">
+        <v>0.99</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1.02</v>
+      </c>
+      <c r="Q9">
+        <v>1</v>
+      </c>
+      <c r="R9" t="str">
+        <v>Inflation domestique, en partie importée.</v>
+      </c>
+      <c r="S9" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>H09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Tarifs transporteurs</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Macroéconomie</v>
+      </c>
+      <c r="D10" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E10" t="str">
+        <v>postes: SOUS_TRAITANCE</v>
+      </c>
+      <c r="F10" t="str">
         <v>Supply chain</v>
       </c>
-      <c r="D4">
-        <v>0.25</v>
-      </c>
-      <c r="E4">
-        <v>0.15</v>
-      </c>
-      <c r="F4">
-        <v>0.25</v>
-      </c>
-      <c r="G4">
-        <v>0.03</v>
-      </c>
-      <c r="H4">
-        <v>0.06</v>
-      </c>
-      <c r="I4" t="str">
-        <v>mois</v>
-      </c>
-      <c r="J4" t="str">
-        <v>volumes Épicerie et Hygiène</v>
-      </c>
-      <c r="K4" t="str">
-        <v>Journal des ruptures : un retard significatif tous les 4 ans en moyenne.</v>
-      </c>
-      <c r="L4" t="str">
+      <c r="G10" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H10" t="str">
+        <v>total</v>
+      </c>
+      <c r="I10">
+        <v>0.995</v>
+      </c>
+      <c r="J10">
+        <v>1.01</v>
+      </c>
+      <c r="K10">
+        <v>1.04</v>
+      </c>
+      <c r="Q10">
+        <v>1</v>
+      </c>
+      <c r="R10" t="str">
+        <v>Renégociation annuelle ; carburant et pièces importés.</v>
+      </c>
+      <c r="S10" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>H10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Masse salariale</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Macroéconomie</v>
+      </c>
+      <c r="D11" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E11" t="str">
+        <v>postes: MASSE_SALARIALE</v>
+      </c>
+      <c r="F11" t="str">
+        <v>RH</v>
+      </c>
+      <c r="G11" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H11" t="str">
+        <v>total</v>
+      </c>
+      <c r="I11">
+        <v>0.995</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>1.015</v>
+      </c>
+      <c r="Q11">
+        <v>1</v>
+      </c>
+      <c r="R11" t="str">
+        <v>Accord salarial signé ; risque de rattrapage en cas d'inflation.</v>
+      </c>
+      <c r="S11" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>H11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Frais commerciaux</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D12" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E12" t="str">
+        <v>postes: FC_VARIABLES, FC_FIXES</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Marketing</v>
+      </c>
+      <c r="G12" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H12" t="str">
+        <v>total</v>
+      </c>
+      <c r="I12">
+        <v>0.97</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>1.04</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12" t="str">
+        <v>Plan promotionnel ; relances possibles si les volumes décrochent.</v>
+      </c>
+      <c r="S12" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>H12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Frais généraux</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Macroéconomie</v>
+      </c>
+      <c r="D13" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E13" t="str">
+        <v>postes: FRAIS_GENERAUX</v>
+      </c>
+      <c r="F13" t="str">
+        <v>DAF</v>
+      </c>
+      <c r="G13" t="str">
+        <v>facteur</v>
+      </c>
+      <c r="H13" t="str">
+        <v>total</v>
+      </c>
+      <c r="I13">
+        <v>0.99</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>1.03</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13" t="str">
+        <v>Énergie, maintenance, informatique : sensibles au change.</v>
+      </c>
+      <c r="S13" t="str">
         <v>valide</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>code</v>
+      </c>
+      <c r="B1" t="str">
+        <v>libelle</v>
+      </c>
+      <c r="C1" t="str">
+        <v>famille</v>
+      </c>
+      <c r="D1" t="str">
+        <v>effet</v>
+      </c>
+      <c r="E1" t="str">
+        <v>sens</v>
+      </c>
+      <c r="F1" t="str">
+        <v>porte_sur</v>
+      </c>
+      <c r="G1" t="str">
+        <v>proprietaire</v>
+      </c>
+      <c r="H1" t="str">
+        <v>p</v>
+      </c>
+      <c r="I1" t="str">
+        <v>amplitude_min</v>
+      </c>
+      <c r="J1" t="str">
+        <v>amplitude_max</v>
+      </c>
+      <c r="K1" t="str">
+        <v>duree</v>
+      </c>
+      <c r="L1" t="str">
+        <v>surcout_min</v>
+      </c>
+      <c r="M1" t="str">
+        <v>surcout_max</v>
+      </c>
+      <c r="N1" t="str">
+        <v>rubrique_surcout</v>
+      </c>
+      <c r="O1" t="str">
+        <v>cible</v>
+      </c>
+      <c r="P1" t="str">
+        <v>justification</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>statut</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>E01</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Révision du prix du carburant</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Macroéconomie</v>
+      </c>
+      <c r="D2" t="str">
+        <v>poste</v>
+      </c>
+      <c r="E2" t="str">
+        <v>hausse</v>
+      </c>
+      <c r="F2" t="str">
+        <v>postes: CARBURANT</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Supply chain</v>
+      </c>
+      <c r="H2">
+        <v>0.35</v>
+      </c>
+      <c r="I2">
+        <v>0.08</v>
+      </c>
+      <c r="J2">
+        <v>0.15</v>
+      </c>
+      <c r="K2" t="str">
+        <v>fin</v>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>carburant de la flotte propre</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Environ 0,4 révision par an sur 5 ans, de +8 % à +15 %.</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>E02</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Perte d'un grand compte GMS</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Commercial</v>
+      </c>
+      <c r="D3" t="str">
+        <v>volume</v>
+      </c>
+      <c r="E3" t="str">
+        <v>baisse</v>
+      </c>
+      <c r="F3" t="str">
+        <v>bu: Boissons, Epicerie</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Directeur commercial</v>
+      </c>
+      <c r="H3">
+        <v>0.15</v>
+      </c>
+      <c r="I3">
+        <v>0.04</v>
+      </c>
+      <c r="J3">
+        <v>0.08</v>
+      </c>
+      <c r="K3" t="str">
+        <v>fin</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v>volumes Boissons et Épicerie</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Deux pertes de comptes en 5 ans, poids de 4 % à 8 % des volumes.</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>E03</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Retard de navire (effet bateau)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Approvisionnement</v>
+      </c>
+      <c r="D4" t="str">
+        <v>volume</v>
+      </c>
+      <c r="E4" t="str">
+        <v>baisse</v>
+      </c>
+      <c r="F4" t="str">
+        <v>bu: Epicerie, Hygiene</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Supply chain</v>
+      </c>
+      <c r="H4">
+        <v>0.25</v>
+      </c>
+      <c r="I4">
+        <v>0.15</v>
+      </c>
+      <c r="J4">
+        <v>0.25</v>
+      </c>
+      <c r="K4" t="str">
+        <v>mois</v>
+      </c>
+      <c r="L4">
+        <v>0.03</v>
+      </c>
+      <c r="M4">
+        <v>0.06</v>
+      </c>
+      <c r="N4" t="str">
+        <v>TR</v>
+      </c>
+      <c r="O4" t="str">
+        <v>volumes Épicerie et Hygiène</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Journal des ruptures : un retard significatif tous les 4 ans en moyenne.</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>valide</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:D19"/>
   <sheetData>
@@ -1751,7 +2500,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F19"/>
   <sheetData>
@@ -2107,9 +2856,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2119,30 +2868,36 @@
         <v>libelle</v>
       </c>
       <c r="C1" t="str">
+        <v>type</v>
+      </c>
+      <c r="D1" t="str">
+        <v>porte_sur</v>
+      </c>
+      <c r="E1" t="str">
         <v>description</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
         <v>hypotheses</v>
       </c>
-      <c r="E1" t="str">
+      <c r="G1" t="str">
         <v>regle</v>
       </c>
-      <c r="F1" t="str">
-        <v>cout_gar</v>
-      </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>cout</v>
+      </c>
+      <c r="I1" t="str">
         <v>cout_libelle</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>mois_effet</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>proprietaire</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>faisabilite</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>parametres</v>
       </c>
     </row>
@@ -2154,30 +2909,36 @@
         <v>Couverture de change</v>
       </c>
       <c r="C2" t="str">
+        <v>couverture</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v>50 % des achats en euros à cours garanti de 5 250</v>
       </c>
-      <c r="D2" t="str">
+      <c r="F2" t="str">
         <v>H06</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <v>Coût matière importé valorisé pour moitié au cours S(t), pour moitié à 5 250</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>implicite dans le cours</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>1</v>
       </c>
-      <c r="I2" t="str">
+      <c r="K2" t="str">
         <v>Trésorerie</v>
       </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Contrat à terme avec la banque</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>part=0.5; cours=5250</v>
       </c>
     </row>
@@ -2189,30 +2950,36 @@
         <v>Hausse tarifaire ciblée</v>
       </c>
       <c r="C3" t="str">
+        <v>prix</v>
+      </c>
+      <c r="D3" t="str">
+        <v>bu: Epicerie, Hygiene</v>
+      </c>
+      <c r="E3" t="str">
         <v>+1 % sur Épicerie et Hygiène au 1er avril, élasticité -0,8</v>
       </c>
-      <c r="D3" t="str">
+      <c r="F3" t="str">
         <v>H02, H03, H04</v>
       </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
         <v>À partir d'avril, prix Épicerie et Hygiène × 1,01 et volumes × 0,992</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>volumes perdus, inclus</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <v>4</v>
       </c>
-      <c r="I3" t="str">
+      <c r="K3" t="str">
         <v>Directeur commercial</v>
       </c>
-      <c r="J3" t="str">
+      <c r="L3" t="str">
         <v>Négociation GMS en mars</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>hausse=0.01; elasticite=-0.8</v>
       </c>
     </row>
@@ -2224,31 +2991,37 @@
         <v>Économies de frais généraux</v>
       </c>
       <c r="C4" t="str">
+        <v>montant</v>
+      </c>
+      <c r="D4" t="str">
+        <v>rubrique: FG</v>
+      </c>
+      <c r="E4" t="str">
         <v>-0,25 GAr en année pleine, effet dès avril</v>
       </c>
-      <c r="D4" t="str">
+      <c r="F4" t="str">
         <v>H12</v>
       </c>
-      <c r="E4" t="str">
+      <c r="G4" t="str">
         <v>Frais généraux diminués de 0,25 / 12 par mois à partir d'avril ; coût unique de 0,05 en janvier</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <v>0.05</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>0,05 GAr, unique</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>4</v>
       </c>
-      <c r="I4" t="str">
+      <c r="K4" t="str">
         <v>DAF</v>
       </c>
-      <c r="J4" t="str">
+      <c r="L4" t="str">
         <v>Plan d'économies identifié</v>
       </c>
-      <c r="K4" t="str">
-        <v>economieAnnuelle=0.25</v>
+      <c r="M4" t="str">
+        <v>variationAnnuelle=-0.25</v>
       </c>
     </row>
     <row r="5">
@@ -2259,30 +3032,36 @@
         <v>Plafond des tarifs transporteurs</v>
       </c>
       <c r="C5" t="str">
+        <v>plafond</v>
+      </c>
+      <c r="D5" t="str">
+        <v>hypothese: H09</v>
+      </c>
+      <c r="E5" t="str">
         <v>Hausses limitées à +3 % contre engagement de volume</v>
       </c>
-      <c r="D5" t="str">
+      <c r="F5" t="str">
         <v>H09</v>
       </c>
-      <c r="E5" t="str">
+      <c r="G5" t="str">
         <v>H09 plafonné à 1,03</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <v>0</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>aucun</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>1</v>
       </c>
-      <c r="I5" t="str">
+      <c r="K5" t="str">
         <v>Supply chain</v>
       </c>
-      <c r="J5" t="str">
+      <c r="L5" t="str">
         <v>Avenant aux contrats transporteurs</v>
       </c>
-      <c r="K5" t="str">
+      <c r="M5" t="str">
         <v>plafond=1.03</v>
       </c>
     </row>
@@ -2294,115 +3073,47 @@
         <v>Stock de sécurité import</v>
       </c>
       <c r="C6" t="str">
+        <v>attenuation</v>
+      </c>
+      <c r="D6" t="str">
+        <v>rubrique: FG ; evenement: E03</v>
+      </c>
+      <c r="E6" t="str">
         <v>+2 semaines de stock, impact de E03 réduit de 75 %</v>
       </c>
-      <c r="D6" t="str">
+      <c r="F6" t="str">
         <v>E03</v>
       </c>
-      <c r="E6" t="str">
+      <c r="G6" t="str">
         <v>Amplitude de E03 × 0,25, surcoût de E03 supprimé, frais généraux + 0,16 / 12 par mois</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <v>0.16</v>
       </c>
-      <c r="G6" t="str">
+      <c r="I6" t="str">
         <v>0,16 GAr par an</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>1</v>
       </c>
-      <c r="I6" t="str">
+      <c r="K6" t="str">
         <v>Supply chain</v>
       </c>
-      <c r="J6" t="str">
+      <c r="L6" t="str">
         <v>Capacité d'entrepôt disponible</v>
       </c>
-      <c r="K6" t="str">
+      <c r="M6" t="str">
         <v>reduction=0.75; coutAnnuel=0.16</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Types : couverture (part, cours) ; prix (hausse, elasticite) ; montant (variationAnnuelle) ; plafond (plafond) ; attenuation (reduction, coutAnnuel).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>code</v>
-      </c>
-      <c r="B1" t="str">
-        <v>libelle</v>
-      </c>
-      <c r="C1" t="str">
-        <v>regle</v>
-      </c>
-      <c r="D1" t="str">
-        <v>mois_effet</v>
-      </c>
-      <c r="E1" t="str">
-        <v>parametres</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>S1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Dépréciation brutale de l'ariary</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Cours +15 % au-dessus de la trajectoire simulée, dès avril</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-      <c r="E2" t="str">
-        <v>choc=0.15</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>S2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Perte de deux grands comptes GMS</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Volumes Boissons et Épicerie -12 % dès avril (E02 forcé)</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3" t="str">
-        <v>choc=0.12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>S3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Choc carburant</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Carburant +25 % dès avril, en plus des révisions simulées</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4" t="str">
-        <v>choc=0.25</v>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M8"/>
   </ignoredErrors>
 </worksheet>
 </file>